--- a/output_data/charts/0500000US39047.xlsx
+++ b/output_data/charts/0500000US39047.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.5445271574303833</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.9934704767254089</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.052631578947368</c:v>
+                  <c:v>1.052522603354269</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.092140734084468</c:v>
+                  <c:v>1.092102989459133</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.196587125416204</c:v>
+                  <c:v>1.226781258663709</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.259673109622792</c:v>
+                  <c:v>1.231313516700774</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.181293864220694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.988558036945134</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>2.106297830513235</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.301984469370146</c:v>
+                  <c:v>2.301746152253433</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.350176263219741</c:v>
+                  <c:v>2.35009504060826</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.299528301886792</c:v>
+                  <c:v>2.276822844469088</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.342367352604366</c:v>
+                  <c:v>2.303076549547362</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.355638941004795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.802453818582851</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.264270167801727</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.336496980155306</c:v>
+                  <c:v>2.339705983849817</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.471141217944287</c:v>
+                  <c:v>2.471055814757215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.521503884572697</c:v>
+                  <c:v>2.533268644302745</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.519346219245584</c:v>
+                  <c:v>2.542402275328639</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.612744076158711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2309070857457954</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2703082215825318</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2864538395168248</c:v>
+                  <c:v>0.2864241838636207</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2730351835211171</c:v>
+                  <c:v>0.2730257473647831</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2774694783573807</c:v>
+                  <c:v>0.2772387025228722</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.263733213033973</c:v>
+                  <c:v>0.2636051472373487</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2744771037453965</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.578439481665288</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.137892297970933</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.150129421915444</c:v>
+                  <c:v>2.1499068258679</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.28796571507569</c:v>
+                  <c:v>2.287886642474512</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.3411487236404</c:v>
+                  <c:v>2.318408649847519</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.373598917305757</c:v>
+                  <c:v>2.33776143734175</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.379959697032868</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>93.85511441963055</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>92.22776100540617</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>91.87230371009491</c:v>
+                  <c:v>91.86969425081097</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>91.5255408861547</c:v>
+                  <c:v>91.5258337653361</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>91.36376248612652</c:v>
+                  <c:v>91.36747990019407</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>91.24128118818753</c:v>
+                  <c:v>91.32184107384413</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>91.19588631783753</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>1.052631578947368</v>
+        <v>1.052522603354269</v>
       </c>
       <c r="C12" s="2">
-        <v>2.301984469370146</v>
+        <v>2.301746152253433</v>
       </c>
       <c r="D12" s="2">
-        <v>2.336496980155306</v>
+        <v>2.339705983849817</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2864538395168248</v>
+        <v>0.2864241838636207</v>
       </c>
       <c r="F12" s="2">
-        <v>2.150129421915444</v>
+        <v>2.1499068258679</v>
       </c>
       <c r="G12" s="2">
-        <v>91.87230371009491</v>
+        <v>91.86969425081097</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>1.092140734084468</v>
+        <v>1.092102989459133</v>
       </c>
       <c r="C13" s="2">
-        <v>2.350176263219741</v>
+        <v>2.35009504060826</v>
       </c>
       <c r="D13" s="2">
-        <v>2.471141217944287</v>
+        <v>2.471055814757215</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2730351835211171</v>
+        <v>0.2730257473647831</v>
       </c>
       <c r="F13" s="2">
-        <v>2.28796571507569</v>
+        <v>2.287886642474512</v>
       </c>
       <c r="G13" s="2">
-        <v>91.5255408861547</v>
+        <v>91.5258337653361</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>1.196587125416204</v>
+        <v>1.226781258663709</v>
       </c>
       <c r="C14" s="2">
-        <v>2.299528301886792</v>
+        <v>2.276822844469088</v>
       </c>
       <c r="D14" s="2">
-        <v>2.521503884572697</v>
+        <v>2.533268644302745</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2774694783573807</v>
+        <v>0.2772387025228722</v>
       </c>
       <c r="F14" s="2">
-        <v>2.3411487236404</v>
+        <v>2.318408649847519</v>
       </c>
       <c r="G14" s="2">
-        <v>91.36376248612652</v>
+        <v>91.36747990019407</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>1.259673109622792</v>
+        <v>1.231313516700774</v>
       </c>
       <c r="C15" s="2">
-        <v>2.342367352604366</v>
+        <v>2.303076549547362</v>
       </c>
       <c r="D15" s="2">
-        <v>2.519346219245584</v>
+        <v>2.542402275328639</v>
       </c>
       <c r="E15" s="2">
-        <v>0.263733213033973</v>
+        <v>0.2636051472373487</v>
       </c>
       <c r="F15" s="2">
-        <v>2.373598917305757</v>
+        <v>2.33776143734175</v>
       </c>
       <c r="G15" s="2">
-        <v>91.24128118818753</v>
+        <v>91.32184107384413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.181293864220694</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.355638941004795</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.612744076158711</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2744771037453965</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.379959697032868</v>
+      </c>
+      <c r="G16" s="2">
+        <v>91.19588631783753</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39047.xlsx
+++ b/output_data/charts/0500000US39047.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.5445271574303833</c:v>
+                  <c:v>0.5445646929068726</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5749913404918601</c:v>
+                  <c:v>0.5750510964076627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6082725060827251</c:v>
+                  <c:v>0.6118121458615775</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6378529104217497</c:v>
+                  <c:v>0.6414278742243603</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7224626553120201</c:v>
+                  <c:v>0.7260034904013961</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7722682321696894</c:v>
+                  <c:v>0.7794205026038936</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.843352500435616</c:v>
+                  <c:v>0.8126961981164981</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8894624856116362</c:v>
+                  <c:v>0.8415098292538148</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.9261200810791921</c:v>
+                  <c:v>0.8829790946846753</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9934704767254089</c:v>
+                  <c:v>0.9360210341805434</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.052522603354269</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.988558036945134</c:v>
+                  <c:v>1.995588336665058</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.98475926567371</c:v>
+                  <c:v>2.009214674195448</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.984706291275635</c:v>
+                  <c:v>2.023151527792262</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.059951202509585</c:v>
+                  <c:v>2.102070696507007</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.048722602261622</c:v>
+                  <c:v>2.108202443280977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.030261732536604</c:v>
+                  <c:v>2.093600363496557</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.070047046523785</c:v>
+                  <c:v>2.13812347401465</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.117269524573581</c:v>
+                  <c:v>2.178847026781662</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.103865240791221</c:v>
+                  <c:v>2.149862143580079</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.106297830513235</c:v>
+                  <c:v>2.145486415425066</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.301746152253433</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.802453818582851</c:v>
+                  <c:v>1.799131453780933</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.766539660547281</c:v>
+                  <c:v>1.770187411230817</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.710114702815433</c:v>
+                  <c:v>1.717245454861473</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.760195189961659</c:v>
+                  <c:v>1.767412675172558</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.954488342873098</c:v>
+                  <c:v>1.965095986038394</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.023272879756788</c:v>
+                  <c:v>2.037677816224529</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.024742986583028</c:v>
+                  <c:v>2.06836414370422</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.092852907321497</c:v>
+                  <c:v>2.133454380390377</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.177255888725798</c:v>
+                  <c:v>2.216172826580113</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.264270167801727</c:v>
+                  <c:v>2.278702892199825</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.339705983849817</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2309070857457954</c:v>
+                  <c:v>0.2309230026883573</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2493938344302044</c:v>
+                  <c:v>0.2494197526587453</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2467848453249913</c:v>
+                  <c:v>0.2502867869433726</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2405019170442663</c:v>
+                  <c:v>0.2440214738897023</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2582716738796593</c:v>
+                  <c:v>0.2617801047120419</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2446098472935667</c:v>
+                  <c:v>0.2481563035196253</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2509147935180345</c:v>
+                  <c:v>0.2546215556330659</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2616066134151872</c:v>
+                  <c:v>0.2688641363176089</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2865730062207311</c:v>
+                  <c:v>0.3001430914738422</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2703082215825318</c:v>
+                  <c:v>0.2909728308501315</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2864241838636207</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.578439481665288</c:v>
+                  <c:v>1.575101675053423</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.621059923796328</c:v>
+                  <c:v>1.61083590258773</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.630170316301703</c:v>
+                  <c:v>1.616435499009282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.697455559428372</c:v>
+                  <c:v>1.69072021195008</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.692726511238308</c:v>
+                  <c:v>1.68586387434555</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.880001397770556</c:v>
+                  <c:v>1.866415015203943</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.996863565081024</c:v>
+                  <c:v>1.967213114754099</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.068436290069413</c:v>
+                  <c:v>2.039177345577709</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.180750681484588</c:v>
+                  <c:v>2.149862143580079</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.137892297970933</c:v>
+                  <c:v>2.099912357581069</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.1499068258679</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>93.85511441963055</c:v>
+                  <c:v>93.85469083890536</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93.80325597506062</c:v>
+                  <c:v>93.78529116291959</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93.81995133819952</c:v>
+                  <c:v>93.78106858553204</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93.60404322063437</c:v>
+                  <c:v>93.55434706825629</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93.32332821443529</c:v>
+                  <c:v>93.25305410122165</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>93.0495859104728</c:v>
+                  <c:v>92.97472999895146</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>92.81407910785852</c:v>
+                  <c:v>92.75898151377747</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>92.57037217900869</c:v>
+                  <c:v>92.53814728167883</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>92.32543510169847</c:v>
+                  <c:v>92.30098070010121</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.22776100540617</c:v>
+                  <c:v>92.24890446976337</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>91.86969425081097</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.5445271574303833</v>
+        <v>0.5445646929068726</v>
       </c>
       <c r="C2" s="2">
-        <v>1.988558036945134</v>
+        <v>1.995588336665058</v>
       </c>
       <c r="D2" s="2">
-        <v>1.802453818582851</v>
+        <v>1.799131453780933</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2309070857457954</v>
+        <v>0.2309230026883573</v>
       </c>
       <c r="F2" s="2">
-        <v>1.578439481665288</v>
+        <v>1.575101675053423</v>
       </c>
       <c r="G2" s="2">
-        <v>93.85511441963055</v>
+        <v>93.85469083890536</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5749913404918601</v>
+        <v>0.5750510964076627</v>
       </c>
       <c r="C3" s="2">
-        <v>1.98475926567371</v>
+        <v>2.009214674195448</v>
       </c>
       <c r="D3" s="2">
-        <v>1.766539660547281</v>
+        <v>1.770187411230817</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2493938344302044</v>
+        <v>0.2494197526587453</v>
       </c>
       <c r="F3" s="2">
-        <v>1.621059923796328</v>
+        <v>1.61083590258773</v>
       </c>
       <c r="G3" s="2">
-        <v>93.80325597506062</v>
+        <v>93.78529116291959</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.6082725060827251</v>
+        <v>0.6118121458615775</v>
       </c>
       <c r="C4" s="2">
-        <v>1.984706291275635</v>
+        <v>2.023151527792262</v>
       </c>
       <c r="D4" s="2">
-        <v>1.710114702815433</v>
+        <v>1.717245454861473</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2467848453249913</v>
+        <v>0.2502867869433726</v>
       </c>
       <c r="F4" s="2">
-        <v>1.630170316301703</v>
+        <v>1.616435499009282</v>
       </c>
       <c r="G4" s="2">
-        <v>93.81995133819952</v>
+        <v>93.78106858553204</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.6378529104217497</v>
+        <v>0.6414278742243603</v>
       </c>
       <c r="C5" s="2">
-        <v>2.059951202509585</v>
+        <v>2.102070696507007</v>
       </c>
       <c r="D5" s="2">
-        <v>1.760195189961659</v>
+        <v>1.767412675172558</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2405019170442663</v>
+        <v>0.2440214738897023</v>
       </c>
       <c r="F5" s="2">
-        <v>1.697455559428372</v>
+        <v>1.69072021195008</v>
       </c>
       <c r="G5" s="2">
-        <v>93.60404322063437</v>
+        <v>93.55434706825629</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.7224626553120201</v>
+        <v>0.7260034904013961</v>
       </c>
       <c r="C6" s="2">
-        <v>2.048722602261622</v>
+        <v>2.108202443280977</v>
       </c>
       <c r="D6" s="2">
-        <v>1.954488342873098</v>
+        <v>1.965095986038394</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2582716738796593</v>
+        <v>0.2617801047120419</v>
       </c>
       <c r="F6" s="2">
-        <v>1.692726511238308</v>
+        <v>1.68586387434555</v>
       </c>
       <c r="G6" s="2">
-        <v>93.32332821443529</v>
+        <v>93.25305410122165</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.7722682321696894</v>
+        <v>0.7794205026038936</v>
       </c>
       <c r="C7" s="2">
-        <v>2.030261732536604</v>
+        <v>2.093600363496557</v>
       </c>
       <c r="D7" s="2">
-        <v>2.023272879756788</v>
+        <v>2.037677816224529</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2446098472935667</v>
+        <v>0.2481563035196253</v>
       </c>
       <c r="F7" s="2">
-        <v>1.880001397770556</v>
+        <v>1.866415015203943</v>
       </c>
       <c r="G7" s="2">
-        <v>93.0495859104728</v>
+        <v>92.97472999895146</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.843352500435616</v>
+        <v>0.8126961981164981</v>
       </c>
       <c r="C8" s="2">
-        <v>2.070047046523785</v>
+        <v>2.13812347401465</v>
       </c>
       <c r="D8" s="2">
-        <v>2.024742986583028</v>
+        <v>2.06836414370422</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2509147935180345</v>
+        <v>0.2546215556330659</v>
       </c>
       <c r="F8" s="2">
-        <v>1.996863565081024</v>
+        <v>1.967213114754099</v>
       </c>
       <c r="G8" s="2">
-        <v>92.81407910785852</v>
+        <v>92.75898151377747</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.8894624856116362</v>
+        <v>0.8415098292538148</v>
       </c>
       <c r="C9" s="2">
-        <v>2.117269524573581</v>
+        <v>2.178847026781662</v>
       </c>
       <c r="D9" s="2">
-        <v>2.092852907321497</v>
+        <v>2.133454380390377</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2616066134151872</v>
+        <v>0.2688641363176089</v>
       </c>
       <c r="F9" s="2">
-        <v>2.068436290069413</v>
+        <v>2.039177345577709</v>
       </c>
       <c r="G9" s="2">
-        <v>92.57037217900869</v>
+        <v>92.53814728167883</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.9261200810791921</v>
+        <v>0.8829790946846753</v>
       </c>
       <c r="C10" s="2">
-        <v>2.103865240791221</v>
+        <v>2.149862143580079</v>
       </c>
       <c r="D10" s="2">
-        <v>2.177255888725798</v>
+        <v>2.216172826580113</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2865730062207311</v>
+        <v>0.3001430914738422</v>
       </c>
       <c r="F10" s="2">
-        <v>2.180750681484588</v>
+        <v>2.149862143580079</v>
       </c>
       <c r="G10" s="2">
-        <v>92.32543510169847</v>
+        <v>92.30098070010121</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.9934704767254089</v>
+        <v>0.9360210341805434</v>
       </c>
       <c r="C11" s="2">
-        <v>2.106297830513235</v>
+        <v>2.145486415425066</v>
       </c>
       <c r="D11" s="2">
-        <v>2.264270167801727</v>
+        <v>2.278702892199825</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2703082215825318</v>
+        <v>0.2909728308501315</v>
       </c>
       <c r="F11" s="2">
-        <v>2.137892297970933</v>
+        <v>2.099912357581069</v>
       </c>
       <c r="G11" s="2">
-        <v>92.22776100540617</v>
+        <v>92.24890446976337</v>
       </c>
     </row>
     <row r="12" spans="1:7">
